--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1563E55E-2CA8-49C0-8DB0-F9AD1C566ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26FD5DE-9D99-4827-BD71-50C2C01ECAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11715" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="7200" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD7BC8-9980-4F3F-8CC7-03B88A271EE4}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -402,22 +402,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
@@ -427,26 +427,112 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A14">
         <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26FD5DE-9D99-4827-BD71-50C2C01ECAAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47600CC8-9C9F-46D1-89C0-C11A0536874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,22 +447,22 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
@@ -472,22 +472,22 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
@@ -497,22 +497,22 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -522,12 +522,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47600CC8-9C9F-46D1-89C0-C11A0536874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE642F3-866C-41B8-934B-53F6773705CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3060" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFD7BC8-9980-4F3F-8CC7-03B88A271EE4}">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
@@ -477,27 +477,27 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
@@ -527,6 +527,371 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100">
         <v>0</v>
       </c>
     </row>

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE642F3-866C-41B8-934B-53F6773705CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D886818-DB0E-4641-856A-146EA765BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,9 +96,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -136,7 +136,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -242,7 +242,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,7 +384,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -667,17 +667,17 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
@@ -697,7 +697,7 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D886818-DB0E-4641-856A-146EA765BF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3AD8D2-4F7B-4ED3-AC37-FAA3F8C0668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -477,12 +477,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
@@ -502,12 +502,12 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
@@ -532,12 +532,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
@@ -577,12 +577,12 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
@@ -667,12 +667,12 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
@@ -682,12 +682,12 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
@@ -697,7 +697,7 @@
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.4">
@@ -707,7 +707,7 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C3AD8D2-4F7B-4ED3-AC37-FAA3F8C0668B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28C26CF-B433-4B9A-8D87-039B34943AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3300" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -487,7 +487,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
@@ -512,7 +512,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -542,7 +542,7 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
@@ -587,7 +587,7 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
@@ -677,7 +677,7 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
@@ -692,7 +692,7 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
@@ -707,12 +707,12 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
@@ -722,7 +722,7 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
@@ -742,7 +742,7 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
@@ -752,47 +752,47 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28C26CF-B433-4B9A-8D87-039B34943AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20E414F-0220-4217-8535-244063793260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,22 +402,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
@@ -487,7 +487,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
@@ -512,7 +512,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -542,7 +542,7 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
@@ -587,7 +587,7 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
@@ -677,7 +677,7 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
@@ -692,7 +692,7 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
@@ -707,12 +707,12 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
@@ -722,7 +722,7 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
@@ -742,7 +742,7 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
@@ -752,47 +752,47 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20E414F-0220-4217-8535-244063793260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2777D284-0D2B-4E7B-8ABC-EF441814D2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -407,17 +407,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
@@ -487,27 +487,27 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
@@ -542,47 +542,47 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
@@ -677,17 +677,17 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
@@ -707,7 +707,7 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2777D284-0D2B-4E7B-8ABC-EF441814D2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28C26CF-B433-4B9A-8D87-039B34943AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3300" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,7 +402,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
@@ -492,27 +492,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
@@ -547,47 +547,47 @@
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.4">
@@ -682,17 +682,17 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.4">
@@ -712,7 +712,7 @@
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.4">
@@ -722,7 +722,7 @@
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.4">
@@ -742,7 +742,7 @@
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.4">
@@ -752,47 +752,47 @@
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A72">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A73">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A75">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A80">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28C26CF-B433-4B9A-8D87-039B34943AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12960605-9859-4921-8573-DEF16E2FBC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3810" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -802,32 +802,32 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12960605-9859-4921-8573-DEF16E2FBC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9DB39-CF07-4956-8588-9A0FFA794FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -812,17 +812,17 @@
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A86">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
@@ -832,7 +832,7 @@
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">

--- a/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
+++ b/ActionGame-リファクタリング-/Data/CSV/Stage/Platform.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\ActionGame-リファクタリング-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B9DB39-CF07-4956-8588-9A0FFA794FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1C7883-86BD-45EF-925A-7B9004E8D800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{A378E325-DACB-423B-896D-A4D927572F7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -852,17 +852,17 @@
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
